--- a/media/file/B0GD1KCH2G/B0GD1KCH2G_ROI-US-pack.xlsx
+++ b/media/file/B0GD1KCH2G/B0GD1KCH2G_ROI-US-pack.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>1849.22</t>
+          <t>643.39</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>1841.85</t>
+          <t>1117.00</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>558.50</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>558.50</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>-133.53</t>
+          <t>-369.02</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-918.66</t>
+          <t>-2538.84</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>-4005.80</t>
+          <t>-11070.52</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>-27559.92</t>
+          <t>-76165.20</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://m.media-amazon.com/images/I/51C3zC3j52L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>196.16</t>
+          <t>35.40</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1022,9 +1022,21 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>1688链接</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>https://aibuy.1688.com/landingpage/home/inventory/products.html?bizType=selectionTool&amp;customerId=sellerspriteLP&amp;lang=zh&amp;currency=CNY</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
@@ -1043,7 +1055,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-47.61</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1066,7 +1078,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-18.02</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1089,7 +1101,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1112,7 +1124,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1135,7 +1147,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">

--- a/media/file/B0GD1KCH2G/B0GD1KCH2G_ROI-US-pack.xlsx
+++ b/media/file/B0GD1KCH2G/B0GD1KCH2G_ROI-US-pack.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>35.23</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>18.47</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>-369.02</t>
+          <t>-314.16</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-2538.84</t>
+          <t>-2133.12</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>18.47</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>-11070.52</t>
+          <t>-9424.68</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>-76165.20</t>
+          <t>-63993.60</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>35.40</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>-47.61</t>
+          <t>-38.04</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>-18.02</t>
+          <t>-15.14</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>39.80</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
